--- a/data/raw/ledger.xlsx
+++ b/data/raw/ledger.xlsx
@@ -1088,28 +1088,23 @@
           <t>0040-1187342-01</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>FT26007GK9WQ</t>
-        </is>
-      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Receipt - Gisenyi Beach Resort - invoice 1044</t>
+          <t>Bank charges - Kivu Commercial Bank</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gisenyi Beach Resort</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>2410550</v>
+        <v>-14500</v>
       </c>
     </row>
     <row r="19">
@@ -1128,21 +1123,21 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bank charges - Kivu Commercial Bank</t>
+          <t>Receipt - Gisenyi Beach Resort - invoice 1043</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>Gisenyi Beach Resort</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6900</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-14500</v>
+        <v>570700</v>
       </c>
     </row>
     <row r="20">
@@ -1159,9 +1154,14 @@
           <t>0040-1187342-01</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>FT26007GK9WQ</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Receipt - Gisenyi Beach Resort - invoice 1043</t>
+          <t>Receipt - Gisenyi Beach Resort - invoice 1044</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>570700</v>
+        <v>2410550</v>
       </c>
     </row>
     <row r="21">
@@ -1949,26 +1949,26 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>AKB753064</t>
+          <t>AKB543814</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Payment - Kigali Fresh Logistics Ltd - delivery services - invoice 1109</t>
+          <t>Receipt - Musanze Tours Ltd - invoice 1107</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kigali Fresh Logistics Ltd</t>
+          <t>Musanze Tours Ltd</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-1390700</v>
+        <v>1849400</v>
       </c>
     </row>
     <row r="42">
@@ -1987,26 +1987,26 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AKB543814</t>
+          <t>AKB753064</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Receipt - Musanze Tours Ltd - invoice 1107</t>
+          <t>Payment - Kigali Fresh Logistics Ltd - delivery services - invoice 1109</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Musanze Tours Ltd</t>
+          <t>Kigali Fresh Logistics Ltd</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>1849400</v>
+        <v>-1390700</v>
       </c>
     </row>
     <row r="43">
@@ -8642,12 +8642,12 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>TX74279671</t>
+          <t>TX38428357</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Receipt - Musanze Tours Ltd - invoice 1186</t>
+          <t>Receipt - Musanze Tours Ltd - invoice 1185</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -8661,7 +8661,7 @@
         </is>
       </c>
       <c r="H222" s="3" t="n">
-        <v>504400</v>
+        <v>170200</v>
       </c>
     </row>
     <row r="223">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>TX38428357</t>
+          <t>TX74279671</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Receipt - Musanze Tours Ltd - invoice 1185</t>
+          <t>Receipt - Musanze Tours Ltd - invoice 1186</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="H223" s="3" t="n">
-        <v>170200</v>
+        <v>504400</v>
       </c>
     </row>
     <row r="224">
